--- a/reports/content/or/2026-05-15_sync_report.xlsx
+++ b/reports/content/or/2026-05-15_sync_report.xlsx
@@ -462,13 +462,13 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>8251</v>
+        <v>8260</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.1% of prev</t>
+          <t>0.0% of prev</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -658,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,303 +695,6 @@
       <c r="G1" t="inlineStr">
         <is>
           <t>after</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>678e3850957f9624888a58dc</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ebceac08-c0cc-49d0-8f68-92cf02b3f94b</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>sentence</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>or</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ମାମା ଓ ମିତା  ଦୁଇ ମିତ।</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>6821b66dea56782698435389</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>6526ab64-39e4-4633-932a-5665de54c7ee</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>paragraph</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>or</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ସେଭଳି ପୋଷାକ ଆଜି ପର୍ଯ୍ୟନ୍ତ କେହି ଦେଖିନଥିବେ। ସେ ହେବ ଏକ ଅଦ୍ଭୁତ ପୋଷାକ। ତା'ର ଏକ ବିଚିତ୍ର ଗୁଣ ହେଉଛି ଏହି ଯେ, ଯେଉଁ ଲୋକ ବୁଦ୍ଧିହୀନ ଏବଂ ନିଜ ଆସନର ଅଯୋଗ୍ୟ ତାହାର ଚକ୍ଷୁକୁ ସେ ବସ୍ତ୍ର ଆଦୌ ଦେଖାଯିବ ନାହିଁ। ରାଜା ଭାବିଲେ, ଏହା ନିଶ୍ଚେ ଏକ ଅଦ୍ଭୁତ ପରିଚ୍ଛଦ ହେବ। ସେ କାରିଗର ଦୁଇ ଜଣଙ୍କୁ ପଚାରିଲେ ଏପରି ଏକ ପରିଚ୍ଛଦ ତିଆରି କରିବାରେ କେତେ ଅର୍ଥ ଖର୍ଚ୍ଚ ହେବ? ଶଠ ଦୁହେଁ ଯେଉଁ ପରିମାଣର ରେଶମସୂତା, ସ୍ଵର୍ଣ୍ଣକରି ଓ ମୋତିମାଣିକ୍ୟର ହିସାବ ଦେଲେ, ତାହା ଶୁଣି ରାଜା ଅଧିକ ଆନନ୍ଦିତ ହେଲେ। ସେ ଭାବିଲେ 'ଏଭଳି ମୂଲ୍ୟବାନ ପୋଷାକ ତ ମୋ' ଭଣ୍ଡାରରେ ନାହିଁ'। ତହୁଁ ସେ କାରିଗର ଦୁହିଁଙ୍କୁ କହିଲେ  ଆଜିଠାରୁ ପନ୍ଦର ଦିନ ମଧ୍ୟରେ ଏହି ପୋଷାକ ସମ୍ପୂର୍ଣ୍ଣ କରି ଆମ୍ଭଙ୍କୁ ଦେବ। ଏହି ମୂଲ୍ୟବାନ ପୋଷାକ ପିନ୍ଧି ଆମ୍ଭେ ଏଥର ଆମ୍ଭ ଜନ୍ମଦିନ ପାଳନ କରିବୁ। ଶଠ ଦୁଇଜଣ ତନ୍ତ ପାଖରେ ବସି ବସ୍ତ୍ର ବୟନର ଛଳନା କଲେ। ରାଜଭଣ୍ଡାରରୁ ଯେତେ ରେଶମ ସୂତା, ସ୍ଵର୍ଣ୍ଣଜରି, ମଣିମାଣିକ୍ୟ ଇତ୍ୟାଦି ପାଇଲେ ସେ ସବୁକୁ ଲୁଚାଇ ରଖିଲେ। ଦିନରାତି ତନ୍ତ ପାଖରେ ବସି ମିଛରେ ବୟନ କରିବା ଭଳି ଅଭିନୟ କଲେ। ଦିନକୁ ଦିନ ସେ ଦୁହିଁଙ୍କୁ ରାଜଭଣ୍ଡାରରୁ ଅଧିକରୁ ଅଧିକ ପରିମାଣର ସ୍ଵର୍ଣ୍ଣଜରି ଓ ମଣିମୁକ୍ତା ଇତ୍ୟାଦି ମିଳିଲା। ଏହି ଅଦ୍ଭୁତ ବସ୍ତ୍ର ଦେଖିବା ପାଇଁ ରାଜାଙ୍କ ମନରେ କ୍ରମେ ଆଗ୍ରହ ବଢ଼ିଲା। କିନ୍ତୁ ତାଙ୍କର ମନେପଡ଼ିଲା ଯେ, କାରିଗର ଦୁହେଁ କହିଛନ୍ତି ନିତାନ୍ତ ବୋକା ଏବଂ ଅଯୋଗ୍ୟ ବ୍ୟକ୍ତିଙ୍କୁ ଏଇ ପୋଷାକ ଦେଖାଯିବ ନାହିଁ। ତେଣୁ ସେ ପ୍ରଥମେ ତାଙ୍କ ପ୍ରଧାନମନ୍ତ୍ରୀଙ୍କୁ ପଠାଇଲେ। ସେତେବେଳକୁ ଏହି ଅଦ୍ଭୁତ ବସ୍ତ୍ର ବିଷୟରେ ରାଜ୍ୟସାରା ପ୍ରଚାର ହୋଇଗଲାଣି। ପ୍ରତ୍ୟେକ ଲୋକ ରାଜାଙ୍କର ଜନ୍ମଦିନ ପାଳନକୁ ଅପେକ୍ଷା କରି ରହିଥାଆନ୍ତି। ପ୍ରଧାନମନ୍ତ୍ରୀ ଯାଇ ଦେଖିଲେ, କାରିଗର ଦୁହେଁ ବସ୍ତ୍ର ବୟନରେ ବ୍ୟସ୍ତ; ଅଥଚ ତନ୍ତଟି ଶୂନ୍ୟ। ସେଥିରେ କୌଣସି ବସ୍ତ୍ର ନାହିଁ। ସେ ଭାବିଲେ, ମୁଁ ତ କାହିଁ ସୂତା ଖିଅଟିଏ ମଧ୍ୟ କେଉଁଠି ଦେଖିବାକୁ ପାଉ ନାହିଁ। ତେବେ କଅଣ ମୁଁ ବୁଦ୍ଧିହୀନ ଓ ପ୍ରଧାନମନ୍ତ୍ରୀ ପଦ ପାଇଁ ଅଯୋଗ୍ୟ। ମନ୍ତ୍ରୀ ଚିନ୍ତାମଗ୍ନ ହୋଇପଡ଼ିବାର ଦେଖୁ ଜଣେ ଶଠ କହିଲା, ପ୍ରଧାନମନ୍ତ୍ରୀ ମହୋଦୟ, ଏ ବସ୍ତ୍ରଟି ଆପଣଙ୍କ ପସନ୍ଦକୁ କିପରି ଆସୁଛି, ତା' ପରେ ସେହି ଶୂନ୍ୟ ତନ୍ତରେ ଅଙ୍ଗୁଳି ଦେଖାଇ କହିଲା, ଏଠାରେ ଏଇ ରଙ୍ଗଟି କିପରି ମାନୁଛି ? ସେଠାରେ ଯେଉଁ ସ୍ୱର୍ଣ୍ଣଜରି ଦିଆଯାଇଛି ଏବଂ ତା' ପାଖରେ ଯେଉଁ ମୁକ୍ତା ଓ ମାଣିକ୍ୟର କଣିକାଗୁଡ଼ିକ ଖଞ୍ଜାଯାଇଛି ତାହା ଆପଣଙ୍କ ମନକୁ ପାଉଛି ତ?</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>6821b66f5bb97d6da470602f</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ab5f3c34-aea2-4b8f-addc-a6792e407a23</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>paragraph</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>or</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ବାପା ଦେଖୁ ଆଶ୍ଚର୍ଯ୍ୟ ହୋଇଗଲେ। ମନେ ମନେ କହି ପକାଇଲେ,  ବାଃ, କେଡ଼େ ସୁନ୍ଦର କବିତା! ସେ ଭାବିଲେ ତାଙ୍କ ଝିଅ ଭବିଷ୍ୟତରେ ନିଶ୍ଚେ ଜଣେ ବଡ଼ କବି ହେବ। କବି ଭାବରେ ନାଆଁ କରିବ।</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>6821b66fea5678269843539b</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>6f0427f6-2e26-4e98-b3bb-3cc4b7e9a307</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>paragraph</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>or</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ଏପରି ସାହାଯ୍ୟକାରୀ ବନ୍ଧୁଟିଏ ଆପଣ ପାଇଲେ କେଉଁଠୁ? ଯୁବକ ଜଣକ ପଚାରିଲେ ସେ ବନ୍ଧୁଟିକୁ ମୋ' ହାତରେ ଟେକି ଦେଇଛନ୍ତି ଆମ ଦେଶର ପୋଲିସ୍ ସଂସ୍ଥା। ଏହି ସଂସ୍ଥା ତରଫରୁ ମୋ' ଭଳି ଚକ୍ଷୁହୀନ ଲୋକମାନଙ୍କୁ ତାଲିମ୍‌ପ୍ରାପ୍ତ କୁକୁରମାନ ଯୋଗାଇ ଦିଆଯାଇ ଥାଏ। ଏହା କହି ଜନ୍ ପକେଟ୍‌ରୁ ଚିଠିଟିଏ ବାହାର କଲେ ଓ ଯୁବକ ଜଣକୁ ଦେଖାଇଲେ। ଚିଠିଟି ଉପରେ ଯୁବକ ଜଣକ ଟିକିଏ ଆଖି ବୁଲେଇ ଆଣିଲେ। କୁକୁର ତାଲିମ୍ ସଂସ୍ଥାର ନିର୍ଦ୍ଦେଶକ ଜନ୍‌ଙ୍କ ପାଖକୁ ଏ ଚିଠିଟି ଲେଖିଥିଲେ। ସେଥିରେ ଲେଖାଥିଲା ପ୍ରିୟବନ୍ଧୁ ଜନ୍, ଡିକ୍ ଆପଣଙ୍କ ସେବାରେ ଯାଉଛି, ମୋର ଆଶା, ସେ ତା'ର ସମସ୍ତ ବୁଦ୍ଧି ଓ କୌଶଳ ଖଟାଇ ଆପଣଙ୍କୁ ସାହାଯ୍ୟ କରିବ। ଆପଣଙ୍କର ଜଣେ ଅନ୍ତରଙ୍ଗ ବନ୍ଧୁ ମଧ୍ୟ ହୋଇପାରିବ।  ବାଃ, ଆପଣଙ୍କ ଦେଶରେ କି ଚମତ୍କାର ବ୍ୟବସ୍ଥା ! ଯୁବକଙ୍କ ତୁଣ୍ଡରୁ ସ୍ଵତଃ ବାହାରିପଡ଼ିଲା। ଯୁବକ ଜଣକ କ୍ଷଣକ ପାଇଁ ଜନ୍‌ଙ୍କ କଳା ଚଷମା ଓ ଡିକ୍‌ର ଉଜ୍ଜଳ ଆଖି ଉପରେ ନଜର ବୁଲାଇ ଆଣିଲେ। ଜନ୍‌ଙ୍କର ସିନା ଆଖି ନାହିଁ, ହେଲେ ଡିକ୍‌ର ତ ଆଖି ଅଛି ! ଡିକ୍‌ର ସେହି ଆଖି କ'ଣ ଜନ୍‌ଙ୍କ ଆଖି ନୁହେଁ।</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>6821b762ea56782698435daa</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>834d05f3-6a37-4308-a830-3d2771f13455</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>sentence</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>or</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ଫୁସ୍‌ଫୁସ୍‌  ଭିତରକୁ ପବନ ନାକ ଓ ଶ୍ଵାସନଳୀ ଦେଇ ଯାଏ ଓ ପୁଣି ସେହି ବାଟେ ବାହାରି ଆସେ।</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6821b77c5bb97d6da4706b49</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>99e8c08d-2b9b-4a62-a10d-5bcf659852cd</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>sentence</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>or</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ଛୁଆ  ଓ ମା'ଭୋକରେ ଥିଲେ।</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>6821b7b3ea56782698436108</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>cd44e93e-d8c3-449d-ad4b-3893861c2106</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>sentence</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>or</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>କାରଣ ରାସ୍ତାରେ ଅନବରତ ଗାଡ଼ିଘୋଡ଼ା ଯା'  ଆସ କରୁଥିଲା।</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>6821b7b5ea5678269843611c</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>e7a33a95-8b7e-4914-9cc3-e050d244fde1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>sentence</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>or</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ଯୁବକ ଜଣକ ପଚାରିଲେ ସେହି ବନ୍ଧୁଟିକୁ ମୋ'  ହାତରେ ଟେକି ଦେଇଛନ୍ତି ଆମ ଦେଶର ପୋଲିସ୍ ସଂସ୍ଥା।</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>6821b7b9ea56782698436146</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>38db2015-80f0-4a78-ae52-49c98122b38b</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>sentence</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>or</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ତାଙ୍କର ପିତା ଅଘୋରନାଥ ଚଟ୍ଟୋପାଧ୍ୟାୟ ଓ ମାତା ବରଦା ସୁନ୍ଦରୀଙ୍କର ସନ୍ତାନମାନଙ୍କ ମଧ୍ୟରେ ସୁଦୀପ  ଥିଲେ ସବୁଠାରୁ ବଡ଼।</t>
         </is>
       </c>
     </row>
